--- a/Test Data/BVT_UK_ImportTB.xlsx
+++ b/Test Data/BVT_UK_ImportTB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ATHENA_Automation_1.0\Workbook_Automation\src\OCT\TestData\SmokeBVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Playwright_self\playwright-OCT-Automation2\Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA19E329-B892-4020-83C9-410546799B09}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630197D2-A726-4575-A5BD-D4294A85B425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{DA4B9D26-82E2-4448-9864-B6C60423C710}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DA4B9D26-82E2-4448-9864-B6C60423C710}"/>
   </bookViews>
   <sheets>
     <sheet name="Trial balance" sheetId="1" r:id="rId1"/>
@@ -166,7 +166,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,6 +178,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -224,9 +230,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -264,7 +270,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -370,7 +376,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -512,7 +518,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1012,6 +1018,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>